--- a/monsters.xlsx
+++ b/monsters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\求职\个人网站开发\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4AEB8EB-3D41-45B1-8690-84296555AD42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C7D6B8E-04C8-416A-A57F-B75FE82468FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9610" yWindow="1130" windowWidth="15990" windowHeight="11190" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6680" yWindow="3600" windowWidth="15990" windowHeight="11190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="怪物" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="152">
   <si>
     <t>怪物</t>
   </si>
@@ -77,9 +77,6 @@
     <t>攻4</t>
   </si>
   <si>
-    <t>攻6</t>
-  </si>
-  <si>
     <t>攻8</t>
   </si>
   <si>
@@ -116,12 +113,6 @@
     <t>狼人</t>
   </si>
   <si>
-    <t>攻11</t>
-  </si>
-  <si>
-    <t>攻13</t>
-  </si>
-  <si>
     <t>火堆</t>
   </si>
   <si>
@@ -137,21 +128,12 @@
     <t>兽人战士</t>
   </si>
   <si>
-    <t>防10</t>
-  </si>
-  <si>
     <t>1个狼人</t>
   </si>
   <si>
     <t>冰霜巨人</t>
   </si>
   <si>
-    <t>防14</t>
-  </si>
-  <si>
-    <t>攻15</t>
-  </si>
-  <si>
     <t>2个哥布林 + 1个黑暗法师</t>
   </si>
   <si>
@@ -164,12 +146,6 @@
     <t>BOSS</t>
   </si>
   <si>
-    <t>攻12</t>
-  </si>
-  <si>
-    <t>攻18</t>
-  </si>
-  <si>
     <t>-</t>
   </si>
   <si>
@@ -185,9 +161,6 @@
     <t>防12</t>
   </si>
   <si>
-    <t>攻20</t>
-  </si>
-  <si>
     <t>一个烈焰术士+一个骷髅战士</t>
   </si>
   <si>
@@ -224,9 +197,6 @@
     <t>造成8伤害</t>
   </si>
   <si>
-    <t>顺劈斩</t>
-  </si>
-  <si>
     <t>对全体造成10伤害</t>
   </si>
   <si>
@@ -387,9 +357,6 @@
   </si>
   <si>
     <t xml:space="preserve">  奖励池概率</t>
-  </si>
-  <si>
-    <t>空白牌10%固定概率，其余所有牌均分90%</t>
   </si>
   <si>
     <t>能力牌刷新</t>
@@ -486,6 +453,58 @@
   </si>
   <si>
     <t>获得4格挡，本关卡中受击反弹4伤害（荆棘效果，使用后在左上角显示出来，可叠加）</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>横扫</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻6</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻5</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻7</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻9</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻11</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻13</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>防8</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>防10</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻15</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>攻18</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>空白牌10%固定概率，其余所有牌（不包括初始牌组）均分90%</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1112,10 +1131,10 @@
         <v>13</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>14</v>
+        <v>141</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>15</v>
+        <v>140</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -1127,12 +1146,12 @@
         <v>1</v>
       </c>
       <c r="M2" s="3" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B3" s="3" t="s">
         <v>12</v>
@@ -1141,13 +1160,13 @@
         <v>35</v>
       </c>
       <c r="D3" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="E3" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="F3" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="F3" s="3" t="s">
-        <v>20</v>
       </c>
       <c r="G3" s="3"/>
       <c r="H3" s="3"/>
@@ -1159,12 +1178,12 @@
         <v>2</v>
       </c>
       <c r="M3" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B4" s="3" t="s">
         <v>12</v>
@@ -1173,13 +1192,13 @@
         <v>28</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="E4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="F4" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="F4" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="G4" s="3"/>
       <c r="H4" s="3"/>
@@ -1190,12 +1209,12 @@
         <v>3</v>
       </c>
       <c r="M4" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="B5" s="3" t="s">
         <v>12</v>
@@ -1204,13 +1223,13 @@
         <v>45</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>20</v>
+        <v>142</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>27</v>
+        <v>143</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -1221,12 +1240,12 @@
         <v>4</v>
       </c>
       <c r="M5" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="3" t="s">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="B6" s="3" t="s">
         <v>12</v>
@@ -1235,13 +1254,13 @@
         <v>32</v>
       </c>
       <c r="D6" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G6" s="3"/>
       <c r="H6" s="3"/>
@@ -1252,12 +1271,12 @@
         <v>5</v>
       </c>
       <c r="M6" s="3" t="s">
-        <v>32</v>
+        <v>29</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="3" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
       <c r="B7" s="3" t="s">
         <v>12</v>
@@ -1266,13 +1285,13 @@
         <v>55</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>34</v>
+        <v>147</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>27</v>
+        <v>145</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>28</v>
+        <v>144</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
@@ -1283,12 +1302,12 @@
         <v>6</v>
       </c>
       <c r="M7" s="3" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="B8" s="3" t="s">
         <v>12</v>
@@ -1297,13 +1316,13 @@
         <v>70</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>37</v>
+        <v>148</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>38</v>
+        <v>146</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="G8" s="3"/>
       <c r="H8" s="3"/>
@@ -1314,12 +1333,12 @@
         <v>7</v>
       </c>
       <c r="M8" s="3" t="s">
-        <v>39</v>
+        <v>33</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="3" t="s">
-        <v>40</v>
+        <v>34</v>
       </c>
       <c r="B9" s="3" t="s">
         <v>12</v>
@@ -1328,13 +1347,13 @@
         <v>40</v>
       </c>
       <c r="D9" s="3" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="G9" s="3"/>
       <c r="H9" s="3"/>
@@ -1345,36 +1364,36 @@
         <v>8</v>
       </c>
       <c r="M9" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="3" t="s">
-        <v>41</v>
+        <v>35</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C10" s="3">
         <v>80</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>43</v>
+        <v>145</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>34</v>
+        <v>147</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>38</v>
+        <v>146</v>
       </c>
       <c r="G10" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>44</v>
+        <v>149</v>
       </c>
       <c r="I10" s="3" t="s">
-        <v>45</v>
+        <v>37</v>
       </c>
       <c r="J10" s="3"/>
       <c r="K10" s="3"/>
@@ -1382,36 +1401,36 @@
         <v>9</v>
       </c>
       <c r="M10" s="3" t="s">
-        <v>46</v>
+        <v>38</v>
       </c>
     </row>
     <row r="11" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="3" t="s">
-        <v>47</v>
+        <v>39</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="C11" s="3">
         <v>100</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>48</v>
+        <v>40</v>
       </c>
       <c r="G11" s="3" t="s">
-        <v>31</v>
+        <v>28</v>
       </c>
       <c r="H11" s="3" t="s">
-        <v>49</v>
+        <v>41</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>50</v>
+        <v>150</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -1419,7 +1438,7 @@
         <v>10</v>
       </c>
       <c r="M11" s="3" t="s">
-        <v>51</v>
+        <v>42</v>
       </c>
     </row>
     <row r="12" spans="1:13" x14ac:dyDescent="0.25">
@@ -1438,7 +1457,7 @@
         <v>11</v>
       </c>
       <c r="M12" s="3" t="s">
-        <v>52</v>
+        <v>43</v>
       </c>
     </row>
     <row r="13" spans="1:13" x14ac:dyDescent="0.25">
@@ -1457,7 +1476,7 @@
         <v>12</v>
       </c>
       <c r="M13" s="3" t="s">
-        <v>53</v>
+        <v>44</v>
       </c>
     </row>
     <row r="14" spans="1:13" x14ac:dyDescent="0.25">
@@ -1476,7 +1495,7 @@
         <v>13</v>
       </c>
       <c r="M14" s="3" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
     </row>
     <row r="15" spans="1:13" x14ac:dyDescent="0.25">
@@ -1495,7 +1514,7 @@
         <v>14</v>
       </c>
       <c r="M15" s="3" t="s">
-        <v>54</v>
+        <v>45</v>
       </c>
     </row>
     <row r="16" spans="1:13" x14ac:dyDescent="0.25">
@@ -1514,7 +1533,7 @@
         <v>15</v>
       </c>
       <c r="M16" s="3" t="s">
-        <v>55</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1537,33 +1556,33 @@
   <sheetData>
     <row r="1" spans="1:5" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="6" t="s">
-        <v>56</v>
+        <v>47</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>57</v>
+        <v>48</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>58</v>
+        <v>49</v>
       </c>
       <c r="E1" s="6" t="s">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="7" t="s">
-        <v>60</v>
+        <v>51</v>
       </c>
       <c r="B2" s="8" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C2" s="7">
         <v>1</v>
       </c>
       <c r="D2" s="9" t="s">
-        <v>62</v>
+        <v>53</v>
       </c>
       <c r="E2" s="7">
         <v>5</v>
@@ -1571,16 +1590,16 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>63</v>
+        <v>139</v>
       </c>
       <c r="B3" s="8" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C3" s="7">
         <v>1</v>
       </c>
       <c r="D3" s="9" t="s">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="E3" s="7">
         <v>5</v>
@@ -1588,16 +1607,16 @@
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="7" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C4" s="7">
         <v>1</v>
       </c>
       <c r="D4" s="9" t="s">
-        <v>66</v>
+        <v>56</v>
       </c>
       <c r="E4" s="7">
         <v>4</v>
@@ -1605,16 +1624,16 @@
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="7" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C5" s="7">
         <v>1</v>
       </c>
       <c r="D5" s="9" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="E5" s="7">
         <v>4</v>
@@ -1622,16 +1641,16 @@
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="7" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="B6" s="8" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C6" s="7">
         <v>1</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="E6" s="7">
         <v>4</v>
@@ -1639,16 +1658,16 @@
     </row>
     <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="7" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C7" s="7">
         <v>1</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="E7" s="7">
         <v>4</v>
@@ -1656,16 +1675,16 @@
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="7" t="s">
-        <v>73</v>
+        <v>63</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C8" s="7">
         <v>1</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="E8" s="7">
         <v>5</v>
@@ -1673,16 +1692,16 @@
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="7" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C9" s="7">
         <v>2</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="E9" s="7">
         <v>3</v>
@@ -1690,16 +1709,16 @@
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="7" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>61</v>
+        <v>52</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="E10" s="7">
         <v>4</v>
@@ -1707,16 +1726,16 @@
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="7" t="s">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C13" s="7">
         <v>1</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>82</v>
+        <v>72</v>
       </c>
       <c r="E13" s="7">
         <v>5</v>
@@ -1724,16 +1743,16 @@
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="7" t="s">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C14" s="7">
         <v>1</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>84</v>
+        <v>74</v>
       </c>
       <c r="E14" s="7">
         <v>4</v>
@@ -1741,16 +1760,16 @@
     </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="7" t="s">
-        <v>85</v>
+        <v>75</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C15" s="7">
         <v>1</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>86</v>
+        <v>76</v>
       </c>
       <c r="E15" s="7">
         <v>5</v>
@@ -1758,16 +1777,16 @@
     </row>
     <row r="16" spans="1:5" ht="47" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>87</v>
+        <v>77</v>
       </c>
       <c r="B16" s="14" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C16" s="13">
         <v>1</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="E16" s="13">
         <v>6</v>
@@ -1775,16 +1794,16 @@
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="16" t="s">
-        <v>88</v>
+        <v>78</v>
       </c>
       <c r="B17" s="18" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C17" s="16">
         <v>1</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="E17" s="16">
         <v>5</v>
@@ -1792,16 +1811,16 @@
     </row>
     <row r="18" spans="1:5" ht="20.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A18" s="19" t="s">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="B18" s="18" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C18" s="19">
         <v>1</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="E18" s="16">
         <v>5</v>
@@ -1809,16 +1828,16 @@
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="19" t="s">
-        <v>91</v>
+        <v>81</v>
       </c>
       <c r="B19" s="18" t="s">
-        <v>81</v>
+        <v>71</v>
       </c>
       <c r="C19" s="19">
         <v>1</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>92</v>
+        <v>82</v>
       </c>
       <c r="E19" s="16">
         <v>5</v>
@@ -1826,70 +1845,70 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C21" s="7">
         <v>2</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="E21" s="7" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>97</v>
+        <v>87</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C22" s="7">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>98</v>
+        <v>88</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>99</v>
+        <v>89</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>94</v>
+        <v>84</v>
       </c>
       <c r="C23" s="7">
         <v>1</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="B26" s="8" t="s">
-        <v>101</v>
+        <v>91</v>
       </c>
       <c r="C26" s="7">
         <v>0</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>102</v>
+        <v>92</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>96</v>
+        <v>86</v>
       </c>
     </row>
   </sheetData>
@@ -1909,40 +1928,40 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
-        <v>103</v>
+        <v>93</v>
       </c>
       <c r="B1" s="10" t="s">
-        <v>104</v>
+        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>105</v>
+        <v>95</v>
       </c>
       <c r="B2" s="12"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
-        <v>106</v>
+        <v>96</v>
       </c>
       <c r="B3" s="12" t="s">
-        <v>107</v>
+        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
-        <v>108</v>
+        <v>98</v>
       </c>
       <c r="B4" s="12" t="s">
-        <v>109</v>
+        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="B5" s="12" t="s">
-        <v>111</v>
+        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1951,32 +1970,32 @@
     </row>
     <row r="7" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>112</v>
+        <v>102</v>
       </c>
       <c r="B7" s="12"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
-        <v>113</v>
+        <v>103</v>
       </c>
       <c r="B8" s="12" t="s">
-        <v>114</v>
+        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
-        <v>115</v>
+        <v>105</v>
       </c>
       <c r="B9" s="12" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>118</v>
+        <v>151</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -1985,32 +2004,32 @@
     </row>
     <row r="12" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="B12" s="12"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="B13" s="12" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="B14" s="12" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="B15" s="12" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2019,24 +2038,24 @@
     </row>
     <row r="17" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="B17" s="12"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="B18" s="12" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -2045,24 +2064,24 @@
     </row>
     <row r="21" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="B21" s="12"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="B22" s="12" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -2071,16 +2090,16 @@
     </row>
     <row r="25" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="11" t="s">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="B25" s="12"/>
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="B26" s="12" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -2089,40 +2108,40 @@
     </row>
     <row r="28" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="B28" s="12"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="B29" s="12" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="B30" s="12" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="B31" s="12" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="B32" s="12" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
     </row>
   </sheetData>

--- a/monsters.xlsx
+++ b/monsters.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Desktop\求职\个人网站开发\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C7D6B8E-04C8-416A-A57F-B75FE82468FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9EC1D9B0-DBC7-4AE3-A015-1D8F484AB305}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6680" yWindow="3600" windowWidth="15990" windowHeight="11190" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6680" yWindow="3600" windowWidth="15990" windowHeight="11190" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="怪物" sheetId="1" r:id="rId1"/>
@@ -281,9 +281,6 @@
     <t>命运轮盘</t>
   </si>
   <si>
-    <t>掷骰：奇数对随机敌人造成5×点数伤害；偶数获得点数×2格挡</t>
-  </si>
-  <si>
     <t>盾反</t>
   </si>
   <si>
@@ -505,6 +502,10 @@
   </si>
   <si>
     <t>空白牌10%固定概率，其余所有牌（不包括初始牌组）均分90%</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>掷骰：奇数对随机敌人造成3×点数伤害；偶数获得点数×2格挡</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1131,10 +1132,10 @@
         <v>13</v>
       </c>
       <c r="E2" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F2" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="G2" s="3"/>
       <c r="H2" s="3"/>
@@ -1223,13 +1224,13 @@
         <v>45</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="E5" s="3" t="s">
+      <c r="F5" s="3" t="s">
         <v>143</v>
-      </c>
-      <c r="F5" s="3" t="s">
-        <v>144</v>
       </c>
       <c r="G5" s="3"/>
       <c r="H5" s="3"/>
@@ -1285,13 +1286,13 @@
         <v>55</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G7" s="3"/>
       <c r="H7" s="3"/>
@@ -1316,10 +1317,10 @@
         <v>70</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F8" s="3" t="s">
         <v>28</v>
@@ -1378,19 +1379,19 @@
         <v>80</v>
       </c>
       <c r="D10" s="3" t="s">
+        <v>144</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="F10" s="3" t="s">
         <v>145</v>
-      </c>
-      <c r="E10" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="F10" s="3" t="s">
-        <v>146</v>
       </c>
       <c r="G10" s="3" t="s">
         <v>22</v>
       </c>
       <c r="H10" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="I10" s="3" t="s">
         <v>37</v>
@@ -1430,7 +1431,7 @@
         <v>41</v>
       </c>
       <c r="I11" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="J11" s="3"/>
       <c r="K11" s="3"/>
@@ -1590,7 +1591,7 @@
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="7" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B3" s="8" t="s">
         <v>52</v>
@@ -1786,7 +1787,7 @@
         <v>1</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E16" s="13">
         <v>6</v>
@@ -1820,7 +1821,7 @@
         <v>1</v>
       </c>
       <c r="D18" s="19" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="E18" s="16">
         <v>5</v>
@@ -1837,7 +1838,7 @@
         <v>1</v>
       </c>
       <c r="D19" s="19" t="s">
-        <v>82</v>
+        <v>151</v>
       </c>
       <c r="E19" s="16">
         <v>5</v>
@@ -1845,70 +1846,70 @@
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="7" t="s">
+        <v>82</v>
+      </c>
+      <c r="B21" s="8" t="s">
         <v>83</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>84</v>
       </c>
       <c r="C21" s="7">
         <v>2</v>
       </c>
       <c r="D21" s="9" t="s">
+        <v>84</v>
+      </c>
+      <c r="E21" s="7" t="s">
         <v>85</v>
-      </c>
-      <c r="E21" s="7" t="s">
-        <v>86</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="7" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="B22" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C22" s="7">
         <v>1</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="E22" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="7" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="B23" s="8" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C23" s="7">
         <v>1</v>
       </c>
       <c r="D23" s="9" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E23" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="7" t="s">
+        <v>89</v>
+      </c>
+      <c r="B26" s="8" t="s">
         <v>90</v>
-      </c>
-      <c r="B26" s="8" t="s">
-        <v>91</v>
       </c>
       <c r="C26" s="7">
         <v>0</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="E26" s="7" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
   </sheetData>
@@ -1928,40 +1929,40 @@
   <sheetData>
     <row r="1" spans="1:2" ht="20" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="B1" s="10" t="s">
         <v>93</v>
-      </c>
-      <c r="B1" s="10" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="11" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="B2" s="12"/>
     </row>
     <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" s="12" t="s">
+        <v>95</v>
+      </c>
+      <c r="B3" s="12" t="s">
         <v>96</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" s="12" t="s">
+        <v>97</v>
+      </c>
+      <c r="B4" s="12" t="s">
         <v>98</v>
-      </c>
-      <c r="B4" s="12" t="s">
-        <v>99</v>
       </c>
     </row>
     <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" s="12" t="s">
+        <v>99</v>
+      </c>
+      <c r="B5" s="12" t="s">
         <v>100</v>
-      </c>
-      <c r="B5" s="12" t="s">
-        <v>101</v>
       </c>
     </row>
     <row r="6" spans="1:2" x14ac:dyDescent="0.25">
@@ -1970,32 +1971,32 @@
     </row>
     <row r="7" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="11" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="B7" s="12"/>
     </row>
     <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" s="12" t="s">
+        <v>102</v>
+      </c>
+      <c r="B8" s="12" t="s">
         <v>103</v>
-      </c>
-      <c r="B8" s="12" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" s="12" t="s">
+        <v>104</v>
+      </c>
+      <c r="B9" s="12" t="s">
         <v>105</v>
-      </c>
-      <c r="B9" s="12" t="s">
-        <v>106</v>
       </c>
     </row>
     <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" s="12" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="B10" s="12" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:2" x14ac:dyDescent="0.25">
@@ -2004,32 +2005,32 @@
     </row>
     <row r="12" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="11" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B12" s="12"/>
     </row>
     <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="s">
+        <v>108</v>
+      </c>
+      <c r="B13" s="12" t="s">
         <v>109</v>
-      </c>
-      <c r="B13" s="12" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="s">
+        <v>110</v>
+      </c>
+      <c r="B14" s="12" t="s">
         <v>111</v>
-      </c>
-      <c r="B14" s="12" t="s">
-        <v>112</v>
       </c>
     </row>
     <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" s="12" t="s">
+        <v>112</v>
+      </c>
+      <c r="B15" s="12" t="s">
         <v>113</v>
-      </c>
-      <c r="B15" s="12" t="s">
-        <v>114</v>
       </c>
     </row>
     <row r="16" spans="1:2" x14ac:dyDescent="0.25">
@@ -2038,24 +2039,24 @@
     </row>
     <row r="17" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A17" s="11" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B17" s="12"/>
     </row>
     <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="B18" s="12" t="s">
         <v>116</v>
-      </c>
-      <c r="B18" s="12" t="s">
-        <v>117</v>
       </c>
     </row>
     <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" s="12" t="s">
+        <v>117</v>
+      </c>
+      <c r="B19" s="12" t="s">
         <v>118</v>
-      </c>
-      <c r="B19" s="12" t="s">
-        <v>119</v>
       </c>
     </row>
     <row r="20" spans="1:2" x14ac:dyDescent="0.25">
@@ -2064,24 +2065,24 @@
     </row>
     <row r="21" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A21" s="11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B21" s="12"/>
     </row>
     <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" s="12" t="s">
+        <v>120</v>
+      </c>
+      <c r="B22" s="12" t="s">
         <v>121</v>
-      </c>
-      <c r="B22" s="12" t="s">
-        <v>122</v>
       </c>
     </row>
     <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" s="12" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B23" s="12" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="24" spans="1:2" x14ac:dyDescent="0.25">
@@ -2096,10 +2097,10 @@
     </row>
     <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="s">
+        <v>123</v>
+      </c>
+      <c r="B26" s="12" t="s">
         <v>124</v>
-      </c>
-      <c r="B26" s="12" t="s">
-        <v>125</v>
       </c>
     </row>
     <row r="27" spans="1:2" x14ac:dyDescent="0.25">
@@ -2108,40 +2109,40 @@
     </row>
     <row r="28" spans="1:2" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="11" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B28" s="12"/>
     </row>
     <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="s">
+        <v>126</v>
+      </c>
+      <c r="B29" s="12" t="s">
         <v>127</v>
-      </c>
-      <c r="B29" s="12" t="s">
-        <v>128</v>
       </c>
     </row>
     <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" s="12" t="s">
+        <v>128</v>
+      </c>
+      <c r="B30" s="12" t="s">
         <v>129</v>
-      </c>
-      <c r="B30" s="12" t="s">
-        <v>130</v>
       </c>
     </row>
     <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="s">
+        <v>130</v>
+      </c>
+      <c r="B31" s="12" t="s">
         <v>131</v>
-      </c>
-      <c r="B31" s="12" t="s">
-        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="B32" s="12" t="s">
         <v>133</v>
-      </c>
-      <c r="B32" s="12" t="s">
-        <v>134</v>
       </c>
     </row>
   </sheetData>
